--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484641_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484641_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0762</v>
+        <v>8.544</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9024</v>
+        <v>8.9986</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8262</v>
+        <v>-0.4546</v>
       </c>
       <c r="G2" t="n">
         <v>9.650499999999999</v>
@@ -610,13 +610,13 @@
         <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.925</v>
+        <v>-0.4572</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3122</v>
+        <v>-0.2161</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6128</v>
+        <v>-0.2412</v>
       </c>
       <c r="V2" t="n">
         <v>0.6335</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>E. CIRCUNS RIVERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9552</v>
+        <v>3.9445</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0509</v>
+        <v>2.4349</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9043</v>
+        <v>1.5097</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1183</v>
+        <v>4.7724</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6439</v>
+        <v>2.2879</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4744</v>
+        <v>2.4845</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3751</v>
+        <v>5.4047</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3749</v>
+        <v>4.0097</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0002</v>
+        <v>1.3949</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2569</v>
+        <v>-0.6323</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7311</v>
+        <v>-1.7219</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4742</v>
+        <v>1.0896</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.6651</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.7805</v>
+        <v>-2.9321</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1154</v>
+        <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8686</v>
+        <v>-0.2781</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8228</v>
+        <v>-0.0377</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0458</v>
+        <v>-0.2404</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4469</v>
+        <v>3.7601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.418</v>
+        <v>0.7065</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0288</v>
+        <v>3.0536</v>
       </c>
       <c r="G4" t="n">
         <v>3.2372</v>
@@ -766,13 +766,13 @@
         <v>2.5656</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0627</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3492</v>
+        <v>-0.0607</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7135</v>
+        <v>-0.6888</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0104</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. CIRCUNS RIVERA</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2874</v>
+        <v>2.6846</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0503</v>
+        <v>-0.526</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2371</v>
+        <v>3.2106</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7724</v>
+        <v>5.1183</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2879</v>
+        <v>2.6439</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4845</v>
+        <v>2.4744</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4047</v>
+        <v>5.3751</v>
       </c>
       <c r="K5" t="n">
-        <v>4.0097</v>
+        <v>4.3749</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3949</v>
+        <v>1.0002</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6323</v>
+        <v>-0.2569</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7219</v>
+        <v>-1.7311</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0896</v>
+        <v>1.4742</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5498</v>
+        <v>-3.6651</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9321</v>
+        <v>-6.7805</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3823</v>
+        <v>3.1154</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9352</v>
+        <v>0.598</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4223</v>
+        <v>0.2459</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5129</v>
+        <v>0.3521</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTAÑES</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2256</v>
+        <v>2.5557</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2256</v>
+        <v>0.2336</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2.3221</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2256</v>
+        <v>0.74</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.3274</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2502</v>
+        <v>1.0673</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2256</v>
+        <v>1.2837</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.0496</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2502</v>
+        <v>0.2341</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.5437</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.3769</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.3467</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.0494</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.3961</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2461</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.2461</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>L. SALVADOR MONTAÑES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1433</v>
+        <v>2.2256</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0549</v>
+        <v>2.2256</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1982</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.74</v>
+        <v>2.2256</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3274</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0673</v>
+        <v>1.2502</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2837</v>
+        <v>2.2256</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0496</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2341</v>
+        <v>1.2502</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5437</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3769</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8332000000000001</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7591</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2391</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2461</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.2461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3376</v>
+        <v>1.0273</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5938</v>
+        <v>0.2092</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7438</v>
+        <v>0.8181</v>
       </c>
       <c r="G8" t="n">
         <v>0.3794</v>
@@ -1078,13 +1078,13 @@
         <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08649999999999999</v>
+        <v>-0.2238</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3107</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2242</v>
+        <v>-0.1499</v>
       </c>
       <c r="V8" t="n">
         <v>0.3219</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2641</v>
+        <v>0.9508</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5978</v>
+        <v>1.3094</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3338</v>
+        <v>-0.3585</v>
       </c>
       <c r="G9" t="n">
         <v>5.086</v>
@@ -1156,13 +1156,13 @@
         <v>2.0158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3326</v>
+        <v>0.0194</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2919</v>
+        <v>0.0034</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0408</v>
+        <v>0.016</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CHALATASHVILI</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5681</v>
+        <v>0.207</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0417</v>
+        <v>-0.3082</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6099</v>
+        <v>0.5152</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1895</v>
+        <v>-0.1264</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1951</v>
+        <v>-0.511</v>
       </c>
       <c r="I11" t="n">
         <v>0.3846</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0217</v>
+        <v>-0.2942</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0217</v>
+        <v>-0.2942</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1303,37 +1303,37 @@
         <v>0.3846</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7897</v>
+        <v>0.2888</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5309</v>
+        <v>-0.0139</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2587</v>
+        <v>0.3028</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3219</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>D. CHALATASHVILI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2595</v>
+        <v>0.1587</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4043</v>
+        <v>-0.4264</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6639</v>
+        <v>0.5851</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1264</v>
+        <v>0.1895</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.511</v>
+        <v>-0.1951</v>
       </c>
       <c r="I12" t="n">
         <v>0.3846</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2942</v>
+        <v>0.0217</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2942</v>
+        <v>0.0217</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1381,31 +1381,31 @@
         <v>0.3846</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3413</v>
+        <v>0.3803</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1101</v>
+        <v>0.1463</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4514</v>
+        <v>0.234</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3219</v>
+        <v>0.3219</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9019</v>
+        <v>-0.5391</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8783</v>
+        <v>-1.5898</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9764</v>
+        <v>1.0507</v>
       </c>
       <c r="G13" t="n">
         <v>0.1889</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6639</v>
+        <v>-0.3011</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3303</v>
+        <v>-0.0418</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3336</v>
+        <v>-0.2593</v>
       </c>
       <c r="V13" t="n">
         <v>1.5889</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2575</v>
+        <v>-1.087</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6525</v>
+        <v>-1.5564</v>
       </c>
       <c r="F14" t="n">
-        <v>0.395</v>
+        <v>0.4693</v>
       </c>
       <c r="G14" t="n">
         <v>-2.1525</v>
@@ -1546,13 +1546,13 @@
         <v>0.3665</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1337</v>
+        <v>0.0368</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1652</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0314</v>
+        <v>0.1058</v>
       </c>
       <c r="V14" t="n">
         <v>1.5785</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.2162</v>
+        <v>-2.244</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.086</v>
+        <v>-1.9898</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1303</v>
+        <v>-0.2541</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1736</v>
@@ -1624,13 +1624,13 @@
         <v>0.1833</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.21</v>
+        <v>-0.2377</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2202</v>
+        <v>-0.1241</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0102</v>
+        <v>-0.1137</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>23.1385</v>
+        <v>23.1384</v>
       </c>
       <c r="E16" t="n">
-        <v>10.6713</v>
+        <v>10.6714</v>
       </c>
       <c r="F16" t="n">
-        <v>12.4671</v>
+        <v>12.4672</v>
       </c>
       <c r="G16" t="n">
         <v>30.0855</v>
@@ -1675,7 +1675,7 @@
         <v>25.6441</v>
       </c>
       <c r="J16" t="n">
-        <v>32.347</v>
+        <v>32.34700000000001</v>
       </c>
       <c r="K16" t="n">
         <v>17.92009999999999</v>
@@ -1702,10 +1702,10 @@
         <v>16.4931</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2709</v>
+        <v>-1.2708</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1923</v>
+        <v>-0.1921999999999999</v>
       </c>
       <c r="U16" t="n">
         <v>-1.0787</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>G. GARCÍA BURGOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0038</v>
+        <v>1.6256</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7337</v>
+        <v>1.6256</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7298</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7378</v>
+        <v>1.6256</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6153</v>
+        <v>1.6256</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3532</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1946</v>
+        <v>1.6256</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1113</v>
+        <v>1.6256</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.9324</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.4365</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9321</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1154</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7441</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6569</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0872</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9346</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.9346</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GARCÍA BURGOS</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6256</v>
+        <v>1.5333</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6256</v>
+        <v>2.0606</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.5273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6256</v>
+        <v>-0.7378</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6256</v>
+        <v>1.6153</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-2.3532</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6256</v>
+        <v>3.1946</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6256</v>
+        <v>3.1113</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-3.9324</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-2.4365</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.9321</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.1154</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.2736</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.0162</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.2898</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9346</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.9346</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0737</v>
+        <v>0.9848</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6418</v>
+        <v>0.4495</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4319</v>
+        <v>0.5353</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7786</v>
@@ -1936,13 +1936,13 @@
         <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3862</v>
+        <v>0.2973</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2557</v>
+        <v>0.0634</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1305</v>
+        <v>0.234</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7054</v>
+        <v>-0.8002</v>
       </c>
       <c r="E21" t="n">
         <v>-0.5237000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1817</v>
+        <v>-0.2765</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0347</v>
@@ -2092,13 +2092,13 @@
         <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7126</v>
+        <v>0.6178</v>
       </c>
       <c r="T21" t="n">
         <v>0.2919</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4207</v>
+        <v>0.326</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7498</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6286</v>
+        <v>-1.4508</v>
       </c>
       <c r="E22" t="n">
         <v>0.0618</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6904</v>
+        <v>-1.5126</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9067</v>
@@ -2170,13 +2170,13 @@
         <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5544</v>
+        <v>-0.3767</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3499</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2045</v>
+        <v>-0.0268</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6335</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0189</v>
+        <v>-2.0437</v>
       </c>
       <c r="E23" t="n">
         <v>-1.8231</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1959</v>
+        <v>-0.2206</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2037</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.313</v>
+        <v>0.2883</v>
       </c>
       <c r="T23" t="n">
         <v>0.3107</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0023</v>
+        <v>-0.0224</v>
       </c>
       <c r="V23" t="n">
         <v>0.3219</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5106</v>
+        <v>-2.3183</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.849</v>
+        <v>-0.6567</v>
       </c>
       <c r="F24" t="n">
         <v>-1.6616</v>
@@ -2326,10 +2326,10 @@
         <v>0.3665</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4216</v>
+        <v>-0.2293</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4404</v>
+        <v>-0.2481</v>
       </c>
       <c r="U24" t="n">
         <v>0.0188</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7914</v>
+        <v>-2.513</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7805</v>
+        <v>-2.3169</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.572</v>
+        <v>-0.1961</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.7596</v>
+        <v>-5.4919</v>
       </c>
       <c r="H25" t="n">
-        <v>3.1732</v>
+        <v>-3.0557</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.9329</v>
+        <v>-2.4362</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8001</v>
+        <v>-2.5457</v>
       </c>
       <c r="K25" t="n">
-        <v>5.9696</v>
+        <v>-1.2637</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.1695</v>
+        <v>-1.2821</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.5597</v>
+        <v>-2.9462</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.7964</v>
+        <v>-1.792</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7633</v>
+        <v>-1.1541</v>
       </c>
       <c r="P25" t="n">
-        <v>1.4661</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.9321</v>
       </c>
       <c r="R25" t="n">
-        <v>4.3982</v>
+        <v>2.7489</v>
       </c>
       <c r="S25" t="n">
-        <v>0.358</v>
+        <v>0.7549</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9126</v>
+        <v>0.3051</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5545</v>
+        <v>0.4498</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.8559</v>
+        <v>2.4072</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.8559</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9092</v>
+        <v>-2.7899</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6053</v>
+        <v>0.2036</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3039</v>
+        <v>-2.9935</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.4919</v>
+        <v>-1.7596</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.0557</v>
+        <v>3.1732</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.4362</v>
+        <v>-4.9329</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.5457</v>
+        <v>2.8001</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.2637</v>
+        <v>5.9696</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.2821</v>
+        <v>-3.1695</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.9462</v>
+        <v>-4.5597</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.792</v>
+        <v>-2.7964</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.1541</v>
+        <v>-1.7633</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1833</v>
+        <v>1.4661</v>
       </c>
       <c r="Q26" t="n">
         <v>-2.9321</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7489</v>
+        <v>4.3982</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3587</v>
+        <v>0.3596</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0166</v>
+        <v>0.3356</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3421</v>
+        <v>0.0239</v>
       </c>
       <c r="V26" t="n">
-        <v>2.4072</v>
+        <v>-2.8559</v>
       </c>
       <c r="W26" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.4486</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.9601</v>
+        <v>-3.1728</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.5623</v>
+        <v>-2.7546</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3978</v>
+        <v>-0.4182</v>
       </c>
       <c r="G27" t="n">
         <v>-4.5842</v>
@@ -2560,13 +2560,13 @@
         <v>2.1991</v>
       </c>
       <c r="S27" t="n">
-        <v>0.7795</v>
+        <v>0.5668</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7127</v>
+        <v>0.5204</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0668</v>
+        <v>0.0464</v>
       </c>
       <c r="V27" t="n">
         <v>-0.4382</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.0996</v>
+        <v>-3.597</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.7583</v>
+        <v>-2.1814</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3413</v>
+        <v>-1.4156</v>
       </c>
       <c r="G28" t="n">
         <v>-3.1149</v>
@@ -2638,13 +2638,13 @@
         <v>1.6493</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.8014</v>
+        <v>-0.2988</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.1938</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.0307</v>
+        <v>-0.105</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>J. CLIMENT GOMIS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2671,73 +2671,73 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.5835</v>
+        <v>-3.9801</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.9211</v>
+        <v>-3.7623</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6624</v>
+        <v>-0.2178</v>
       </c>
       <c r="G29" t="n">
-        <v>-4.0744</v>
+        <v>-4.7823</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0037</v>
+        <v>-3.5035</v>
       </c>
       <c r="I29" t="n">
-        <v>-4.0707</v>
+        <v>-1.2789</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6384</v>
+        <v>-1.804</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5668</v>
+        <v>-1.8397</v>
       </c>
       <c r="L29" t="n">
-        <v>-3.2051</v>
+        <v>0.0356</v>
       </c>
       <c r="M29" t="n">
-        <v>-3.4361</v>
+        <v>-2.9783</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.5704</v>
+        <v>-1.6638</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.8656</v>
+        <v>-1.3145</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="Q29" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R29" t="n">
-        <v>3.2986</v>
+        <v>2.7489</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3061</v>
+        <v>-0.2805</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3824</v>
+        <v>-0.4189</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.1384</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.4486</v>
+        <v>-0.7498</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.4486</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>J. CLIMENT GOMIS</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2749,67 +2749,67 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.6095</v>
+        <v>-4.3096</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.2431</v>
+        <v>-3.825</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3664</v>
+        <v>-0.4846</v>
       </c>
       <c r="G30" t="n">
-        <v>-4.7823</v>
+        <v>-4.0744</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.5035</v>
+        <v>-0.0037</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.2789</v>
+        <v>-4.0707</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.804</v>
+        <v>-0.6384</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.8397</v>
+        <v>2.5668</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0356</v>
+        <v>-3.2051</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.9783</v>
+        <v>-3.4361</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.6638</v>
+        <v>-2.5704</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.3145</v>
+        <v>-0.8656</v>
       </c>
       <c r="P30" t="n">
-        <v>1.8326</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R30" t="n">
-        <v>2.7489</v>
+        <v>3.2986</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.9099</v>
+        <v>0.58</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.8997000000000001</v>
+        <v>0.4785</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.0103</v>
+        <v>0.1014</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.7498</v>
+        <v>-0.4486</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.1267</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="31">
@@ -2827,19 +2827,19 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-23.1384</v>
+        <v>-21.8564</v>
       </c>
       <c r="E31" t="n">
-        <v>-12.4672</v>
+        <v>-12.4673</v>
       </c>
       <c r="F31" t="n">
-        <v>-10.6713</v>
+        <v>-9.389100000000001</v>
       </c>
       <c r="G31" t="n">
         <v>-30.0852</v>
       </c>
       <c r="H31" t="n">
-        <v>-4.4414</v>
+        <v>-4.441400000000001</v>
       </c>
       <c r="I31" t="n">
         <v>-25.6442</v>
@@ -2872,13 +2872,13 @@
         <v>26.5724</v>
       </c>
       <c r="S31" t="n">
-        <v>1.2709</v>
+        <v>2.553</v>
       </c>
       <c r="T31" t="n">
-        <v>1.0788</v>
+        <v>1.0787</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1921000000000001</v>
+        <v>1.4743</v>
       </c>
       <c r="V31" t="n">
         <v>-4.4032</v>
@@ -2887,7 +2887,7 @@
         <v>0.6855000000000002</v>
       </c>
       <c r="X31" t="n">
-        <v>-5.0886</v>
+        <v>-5.088599999999999</v>
       </c>
     </row>
   </sheetData>
